--- a/import/tb_brand2.xlsx
+++ b/import/tb_brand2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CFFF60-A076-4DD8-A5ED-65D5C3817014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE6E32F-C785-41DF-9B11-C03AB9BFDED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Daihatsu,Jaecoo,Icar</t>
+  </si>
+  <si>
+    <t>priority_brand</t>
   </si>
 </sst>
 </file>
@@ -451,16 +454,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,8 +477,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -485,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -499,7 +506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -513,7 +520,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -524,7 +531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -535,7 +542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -546,7 +553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -560,7 +567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -574,7 +581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -588,7 +595,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -602,7 +609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -613,7 +620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -627,7 +634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -641,7 +648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -652,7 +659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>

--- a/import/tb_brand2.xlsx
+++ b/import/tb_brand2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE6E32F-C785-41DF-9B11-C03AB9BFDED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F63672-2D37-48B4-A47B-2780E3FBFDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Jaecoo</t>
   </si>
   <si>
-    <t>Icar</t>
-  </si>
-  <si>
     <t>Geely Group</t>
   </si>
   <si>
@@ -100,16 +97,31 @@
     <t>ASFIN,Vinfast</t>
   </si>
   <si>
-    <t>Lexus,Jetour</t>
-  </si>
-  <si>
     <t>Suzuki,Lepas</t>
   </si>
   <si>
-    <t>Daihatsu,Jaecoo,Icar</t>
-  </si>
-  <si>
     <t>priority_brand</t>
+  </si>
+  <si>
+    <t>Toyota,Lexus,Jetour</t>
+  </si>
+  <si>
+    <t>ICAR</t>
+  </si>
+  <si>
+    <t>Lexus,Jetour,6B</t>
+  </si>
+  <si>
+    <t>Daihatsu,ICAR,Chery</t>
+  </si>
+  <si>
+    <t>Suzuki,Wuling,Jaecoo,Lepas</t>
+  </si>
+  <si>
+    <t>Suzuki,Jaecoo,Lepas</t>
+  </si>
+  <si>
+    <t>ICAR,Chery</t>
   </si>
 </sst>
 </file>
@@ -458,10 +470,10 @@
   <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -478,7 +490,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -491,6 +503,12 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -503,7 +521,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -517,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -530,6 +548,9 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -564,7 +585,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -578,7 +602,10 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -586,13 +613,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -600,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -614,7 +641,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -625,13 +652,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -642,10 +669,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -653,10 +683,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -667,7 +700,10 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -675,10 +711,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -686,10 +722,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -697,13 +736,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
